--- a/data_templates/input_parameter_temp.xlsx
+++ b/data_templates/input_parameter_temp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mohammedfaran/Desktop/python_models/ReactorModels/data_in_templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/pfas_modeling/reactormodels/data_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E665311C-773D-A244-A8EC-DE6C4A9843D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7999E112-C8F5-6444-8C87-69D2E3E0C36F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{8FC1EBE6-09F5-E544-BEAB-0C438D750464}"/>
+    <workbookView xWindow="7000" yWindow="1040" windowWidth="28800" windowHeight="18000" xr2:uid="{8FC1EBE6-09F5-E544-BEAB-0C438D750464}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="72">
   <si>
     <t>water</t>
   </si>
@@ -99,9 +99,6 @@
     <t>porosity</t>
   </si>
   <si>
-    <t>bulk_density</t>
-  </si>
-  <si>
     <t>sorbent_mass</t>
   </si>
   <si>
@@ -235,9 +232,6 @@
   </si>
   <si>
     <t xml:space="preserve">Packed-bed porosity: fraction of the total bed volume occupied by fluid-filled pore space between media particles. </t>
-  </si>
-  <si>
-    <t>Bulk density of the packed sorbent: total sorbent mass divided by total packed-bed volume.</t>
   </si>
   <si>
     <t>Molar mass of the chemical. Dimesnions are [M/mol].</t>
@@ -451,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -540,66 +534,65 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="11" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -935,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1156A5E6-1152-6E4D-AE94-8617611FAF4C}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" style="7" bestFit="1" customWidth="1"/>
@@ -948,24 +941,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="21"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="31" t="s">
-        <v>50</v>
+      <c r="C1" s="33"/>
+      <c r="D1"/>
+      <c r="E1" s="29" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="31" t="s">
-        <v>44</v>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="29" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -976,13 +969,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -990,12 +983,12 @@
         <v>3</v>
       </c>
       <c r="B4" s="9"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="32" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="22"/>
-      <c r="E4" s="31" t="s">
-        <v>45</v>
+      <c r="E4" s="29" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1003,12 +996,12 @@
         <v>5</v>
       </c>
       <c r="B5" s="9"/>
-      <c r="C5" s="34" t="s">
-        <v>29</v>
+      <c r="C5" s="32" t="s">
+        <v>28</v>
       </c>
       <c r="D5" s="22"/>
-      <c r="E5" s="31" t="s">
-        <v>55</v>
+      <c r="E5" s="29" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1016,12 +1009,12 @@
         <v>6</v>
       </c>
       <c r="B6" s="9"/>
-      <c r="C6" s="34" t="s">
-        <v>30</v>
+      <c r="C6" s="32" t="s">
+        <v>29</v>
       </c>
       <c r="D6" s="22"/>
-      <c r="E6" s="31" t="s">
-        <v>56</v>
+      <c r="E6" s="29" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1029,23 +1022,23 @@
         <v>7</v>
       </c>
       <c r="B7" s="9"/>
-      <c r="C7" s="34" t="s">
-        <v>32</v>
+      <c r="C7" s="32" t="s">
+        <v>31</v>
       </c>
       <c r="D7" s="22"/>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="29" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="31" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1056,199 +1049,186 @@
         <v>10</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="9"/>
-      <c r="C10" s="34" t="s">
-        <v>29</v>
+      <c r="C10" s="32" t="s">
+        <v>4</v>
       </c>
       <c r="D10" s="22"/>
-      <c r="E10" s="31" t="s">
-        <v>59</v>
+      <c r="E10" s="29" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="9"/>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="32" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="22"/>
-      <c r="E11" s="31" t="s">
-        <v>46</v>
+      <c r="E11" s="29" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" s="9"/>
-      <c r="C12" s="34" t="s">
-        <v>4</v>
+      <c r="C12" s="32" t="s">
+        <v>28</v>
       </c>
       <c r="D12" s="22"/>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="29" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="9"/>
-      <c r="C13" s="34" t="s">
-        <v>29</v>
+      <c r="C13" s="32" t="s">
+        <v>30</v>
       </c>
       <c r="D13" s="22"/>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="29" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="25" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="B14" s="9"/>
-      <c r="C14" s="34" t="s">
-        <v>31</v>
+      <c r="C14" s="32" t="s">
+        <v>30</v>
       </c>
       <c r="D14" s="22"/>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="29" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="31" t="s">
+      <c r="A15" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="22"/>
+      <c r="E17" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="23"/>
+      <c r="C18" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="22"/>
+      <c r="E18" s="29" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="31" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="31" t="s">
+      <c r="F18" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="23"/>
+      <c r="C19" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="22"/>
+      <c r="E19" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="22"/>
+      <c r="E20" s="29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="23"/>
+      <c r="C21" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="22"/>
+      <c r="E21" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="37" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19" s="37" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="22"/>
-      <c r="E21" s="31" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="22"/>
-      <c r="E22" s="31" t="s">
-        <v>49</v>
-      </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="3">
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A8:D8"/>
   </mergeCells>
@@ -1286,38 +1266,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="38" t="s">
+      <c r="D1" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="E1" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="40" t="s">
+      <c r="G1" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="H1" s="35" t="s">
         <v>26</v>
-      </c>
-      <c r="H1" s="38" t="s">
-        <v>27</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="41" t="s">
+      <c r="L1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="42" t="s">
-        <v>52</v>
+      <c r="M1" s="39" t="s">
+        <v>51</v>
       </c>
       <c r="N1" s="2"/>
       <c r="O1" s="3"/>
@@ -1335,7 +1315,7 @@
     </row>
     <row r="2" spans="1:26" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="10"/>
@@ -1344,11 +1324,11 @@
       <c r="F2" s="12"/>
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
-      <c r="L2" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="44" t="s">
-        <v>53</v>
+      <c r="L2" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="41" t="s">
+        <v>52</v>
       </c>
       <c r="N2" s="13"/>
       <c r="O2" s="14"/>
@@ -1360,7 +1340,7 @@
     </row>
     <row r="3" spans="1:26" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -1372,11 +1352,11 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
-      <c r="L3" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="46" t="s">
-        <v>69</v>
+      <c r="L3" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" s="43" t="s">
+        <v>67</v>
       </c>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
@@ -1394,7 +1374,7 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1406,11 +1386,11 @@
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
       <c r="K4" s="19"/>
-      <c r="L4" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" s="48" t="s">
-        <v>67</v>
+      <c r="L4" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="45" t="s">
+        <v>65</v>
       </c>
       <c r="N4" s="19"/>
       <c r="O4" s="19"/>
@@ -1428,7 +1408,7 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -1440,11 +1420,11 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
-      <c r="L5" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="46" t="s">
-        <v>70</v>
+      <c r="L5" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="43" t="s">
+        <v>68</v>
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
@@ -1462,7 +1442,7 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -1474,11 +1454,11 @@
       <c r="I6" s="20"/>
       <c r="J6" s="20"/>
       <c r="K6" s="20"/>
-      <c r="L6" s="49" t="s">
+      <c r="L6" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="M6" s="50" t="s">
-        <v>71</v>
+      <c r="M6" s="47" t="s">
+        <v>69</v>
       </c>
       <c r="N6" s="20"/>
       <c r="O6" s="20"/>
@@ -1496,7 +1476,7 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -1508,11 +1488,11 @@
       <c r="I7" s="20"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
-      <c r="L7" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="46" t="s">
-        <v>72</v>
+      <c r="L7" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="43" t="s">
+        <v>70</v>
       </c>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
@@ -1530,7 +1510,7 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -1542,11 +1522,11 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
-      <c r="L8" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8" s="46" t="s">
-        <v>73</v>
+      <c r="L8" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="43" t="s">
+        <v>71</v>
       </c>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
@@ -1570,11 +1550,11 @@
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
       <c r="H9" s="6"/>
-      <c r="L9" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="44" t="s">
-        <v>68</v>
+      <c r="L9" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="41" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
